--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B75D36-960B-4A31-A1DE-3E6D620BED93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E710A97-28BE-47D3-87D7-1AB664715363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,10 +690,10 @@
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="out_of_scope_reason"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="year_of_income_being_tested"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Status">
-      <calculatedColumnFormula>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Floor_year">
-      <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Floor_rate">
       <calculatedColumnFormula>IFERROR(INDEX(tblRates[rate],MATCH(tblLoans[[#This Row],[Floor_year]],tblRates[year_of_income],0)),"")</calculatedColumnFormula>
@@ -729,10 +729,10 @@
       <calculatedColumnFormula>IF(AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),ISNUMBER(Summary!$B$3),Summary!$B$3&gt;0,ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&gt;0),ROUND(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]*Summary!$B$3/(1-(1/(1+Summary!$B$3))^tblLoans[[#This Row],[Term_used]]),2),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="MYR_verdict">
-      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="MYR_reason">
-      <calculatedColumnFormula>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="MYR_required">
       <calculatedColumnFormula>IF(OR(tblLoans[[#This Row],[MYR_verdict]]="MYR_MET",tblLoans[[#This Row],[MYR_verdict]]="MYR_SHORT"),tblLoans[[#This Row],[MYR_raw]],"")</calculatedColumnFormula>
@@ -750,7 +750,7 @@
       <calculatedColumnFormula>IF(OR(_xlfn.ISFORMULA(tblLoans[[#This Row],[loan_id]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[borrower_reference]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[year_loan_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[written_agreement]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[maximum_term_years]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[security_coverage_at_first_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[remaining_term_years]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[payments_applied_during_the_year]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[out_of_scope_reason]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[year_of_income_being_tested]])),1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Input_problem">
-      <calculatedColumnFormula>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Sample_row">
       <calculatedColumnFormula>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</calculatedColumnFormula>
@@ -1300,11 +1300,11 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P2" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2023-24</v>
       </c>
       <c r="Q2" s="9">
@@ -1352,11 +1352,11 @@
         <v>47212.37</v>
       </c>
       <c r="AB2" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>MYR_SHORT</v>
       </c>
       <c r="AC2" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD2" s="10">
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ2" s="9">
@@ -1428,11 +1428,11 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P3" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2022-23</v>
       </c>
       <c r="Q3" s="9">
@@ -1480,11 +1480,11 @@
         <v>27640.06</v>
       </c>
       <c r="AB3" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC3" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is NOT_COMPLYING, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD3" s="10" t="str">
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ3" s="9">
@@ -1556,11 +1556,11 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P4" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2021-22</v>
       </c>
       <c r="Q4" s="9">
@@ -1608,11 +1608,11 @@
         <v>28334.799999999999</v>
       </c>
       <c r="AB4" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC4" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is UNKNOWN, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD4" s="10" t="str">
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ4" s="9">
@@ -1684,11 +1684,11 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P5" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2024-25</v>
       </c>
       <c r="Q5" s="9">
@@ -1736,11 +1736,11 @@
         <v>22489.279999999999</v>
       </c>
       <c r="AB5" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>UNKNOWN</v>
       </c>
       <c r="AC5" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>payments applied not established</v>
       </c>
       <c r="AD5" s="10" t="str">
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ5" s="9">
@@ -1812,11 +1812,11 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P6" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2019-20</v>
       </c>
       <c r="Q6" s="9">
@@ -1864,11 +1864,11 @@
         <v/>
       </c>
       <c r="AB6" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC6" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>nil remaining term under s 109E(6)</v>
       </c>
       <c r="AD6" s="10" t="str">
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ6" s="9">
@@ -1940,11 +1940,11 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P7" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2020-21</v>
       </c>
       <c r="Q7" s="9">
@@ -1992,11 +1992,11 @@
         <v>36713.81</v>
       </c>
       <c r="AB7" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC7" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is NOT_COMPLYING, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD7" s="10" t="str">
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ7" s="9">
@@ -2070,11 +2070,11 @@
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>SKIPPED</v>
       </c>
       <c r="P8" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2023-24</v>
       </c>
       <c r="Q8" s="9">
@@ -2122,11 +2122,11 @@
         <v/>
       </c>
       <c r="AB8" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v/>
       </c>
       <c r="AC8" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD8" s="10" t="str">
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ8" s="9">
@@ -2198,11 +2198,11 @@
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>SKIPPED</v>
       </c>
       <c r="P9" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>1996-97</v>
       </c>
       <c r="Q9" s="9" t="str">
@@ -2250,11 +2250,11 @@
         <v/>
       </c>
       <c r="AB9" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v/>
       </c>
       <c r="AC9" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD9" s="10" t="str">
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ9" s="9">

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E710A97-28BE-47D3-87D7-1AB664715363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD8E472-22D5-4F8F-BA8B-5147CC4BEA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -750,7 +750,7 @@
       <calculatedColumnFormula>IF(OR(_xlfn.ISFORMULA(tblLoans[[#This Row],[loan_id]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[borrower_reference]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[year_loan_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[written_agreement]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[maximum_term_years]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[security_coverage_at_first_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[remaining_term_years]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[payments_applied_during_the_year]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[out_of_scope_reason]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[year_of_income_being_tested]])),1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Input_problem">
-      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Sample_row">
       <calculatedColumnFormula>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</calculatedColumnFormula>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ2" s="9">
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ3" s="9">
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ4" s="9">
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ5" s="9">
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ6" s="9">
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ7" s="9">
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ8" s="9">
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)-N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ABS(ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)-N(tblLoans[[#This Row],[payments_applied_during_the_year]]))&gt;0.0000001,N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ9" s="9">

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B75D36-960B-4A31-A1DE-3E6D620BED93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD8E472-22D5-4F8F-BA8B-5147CC4BEA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,10 +690,10 @@
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="out_of_scope_reason"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="year_of_income_being_tested"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Status">
-      <calculatedColumnFormula>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Floor_year">
-      <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Floor_rate">
       <calculatedColumnFormula>IFERROR(INDEX(tblRates[rate],MATCH(tblLoans[[#This Row],[Floor_year]],tblRates[year_of_income],0)),"")</calculatedColumnFormula>
@@ -729,10 +729,10 @@
       <calculatedColumnFormula>IF(AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),ISNUMBER(Summary!$B$3),Summary!$B$3&gt;0,ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&gt;0),ROUND(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]*Summary!$B$3/(1-(1/(1+Summary!$B$3))^tblLoans[[#This Row],[Term_used]]),2),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="MYR_verdict">
-      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="MYR_reason">
-      <calculatedColumnFormula>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="MYR_required">
       <calculatedColumnFormula>IF(OR(tblLoans[[#This Row],[MYR_verdict]]="MYR_MET",tblLoans[[#This Row],[MYR_verdict]]="MYR_SHORT"),tblLoans[[#This Row],[MYR_raw]],"")</calculatedColumnFormula>
@@ -750,7 +750,7 @@
       <calculatedColumnFormula>IF(OR(_xlfn.ISFORMULA(tblLoans[[#This Row],[loan_id]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[borrower_reference]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[year_loan_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[written_agreement]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[maximum_term_years]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[security_coverage_at_first_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[remaining_term_years]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[payments_applied_during_the_year]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[out_of_scope_reason]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[year_of_income_being_tested]])),1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Input_problem">
-      <calculatedColumnFormula>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Sample_row">
       <calculatedColumnFormula>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</calculatedColumnFormula>
@@ -1300,11 +1300,11 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P2" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2023-24</v>
       </c>
       <c r="Q2" s="9">
@@ -1352,11 +1352,11 @@
         <v>47212.37</v>
       </c>
       <c r="AB2" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>MYR_SHORT</v>
       </c>
       <c r="AC2" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD2" s="10">
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ2" s="9">
@@ -1428,11 +1428,11 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P3" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2022-23</v>
       </c>
       <c r="Q3" s="9">
@@ -1480,11 +1480,11 @@
         <v>27640.06</v>
       </c>
       <c r="AB3" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC3" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is NOT_COMPLYING, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD3" s="10" t="str">
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ3" s="9">
@@ -1556,11 +1556,11 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P4" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2021-22</v>
       </c>
       <c r="Q4" s="9">
@@ -1608,11 +1608,11 @@
         <v>28334.799999999999</v>
       </c>
       <c r="AB4" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC4" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is UNKNOWN, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD4" s="10" t="str">
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ4" s="9">
@@ -1684,11 +1684,11 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P5" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2024-25</v>
       </c>
       <c r="Q5" s="9">
@@ -1736,11 +1736,11 @@
         <v>22489.279999999999</v>
       </c>
       <c r="AB5" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>UNKNOWN</v>
       </c>
       <c r="AC5" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>payments applied not established</v>
       </c>
       <c r="AD5" s="10" t="str">
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ5" s="9">
@@ -1812,11 +1812,11 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P6" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2019-20</v>
       </c>
       <c r="Q6" s="9">
@@ -1864,11 +1864,11 @@
         <v/>
       </c>
       <c r="AB6" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC6" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>nil remaining term under s 109E(6)</v>
       </c>
       <c r="AD6" s="10" t="str">
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ6" s="9">
@@ -1940,11 +1940,11 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P7" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2020-21</v>
       </c>
       <c r="Q7" s="9">
@@ -1992,11 +1992,11 @@
         <v>36713.81</v>
       </c>
       <c r="AB7" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC7" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is NOT_COMPLYING, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD7" s="10" t="str">
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ7" s="9">
@@ -2070,11 +2070,11 @@
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>SKIPPED</v>
       </c>
       <c r="P8" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>2023-24</v>
       </c>
       <c r="Q8" s="9">
@@ -2122,11 +2122,11 @@
         <v/>
       </c>
       <c r="AB8" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v/>
       </c>
       <c r="AC8" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD8" s="10" t="str">
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ8" s="9">
@@ -2198,11 +2198,11 @@
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="9" t="str">
-        <f>IF(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>SKIPPED</v>
       </c>
       <c r="P9" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[year_loan_made]]&amp;"",tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"")</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
         <v>1996-97</v>
       </c>
       <c r="Q9" s="9" t="str">
@@ -2250,11 +2250,11 @@
         <v/>
       </c>
       <c r="AB9" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;""),tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v/>
       </c>
       <c r="AC9" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[year_loan_made]]&amp;"","gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[year_loan_made]]&amp;""=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD9" s="10" t="str">
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="9" t="str">
-        <f>TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_loan_made]])=7,MID(tblLoans[[#This Row],[year_loan_made]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_loan_made]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_loan_made]],4))+1,100)),FALSE))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[year_of_income_being_tested]])=7,MID(tblLoans[[#This Row],[year_of_income_being_tested]],5,1)="-",ISNUMBER(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))),ISNUMBER(VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))),VALUE(RIGHT(tblLoans[[#This Row],[year_of_income_being_tested]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[year_of_income_being_tested]],4))+1,100)),FALSE)))),"year label ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0))))),"number ",""))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ9" s="9">

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD8E472-22D5-4F8F-BA8B-5147CC4BEA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA084D99-9AAC-4EBC-B672-6DE10659BCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -401,7 +401,7 @@
     <t>No formula in an input cell</t>
   </si>
   <si>
-    <t>A reviewed benchmark rate exists for the year of income</t>
+    <t>A reviewed benchmark exists and every table rate is a number from zero to one</t>
   </si>
   <si>
     <t>Every reviewed loan is on s 109N terms</t>
@@ -422,7 +422,7 @@
     <t>Caveats the engine attaches to every result</t>
   </si>
   <si>
-    <t>COMPLYING means the four limbs of s 109N(1) are established on the operator's own facts. The lodgment day (s 109D(6)) is asserted, not computed. Refinancing reductions to the maximum term (s 109N(3A) to (3D)) and the other Subdivision D exclusions are not modelled.</t>
+    <t>Interest-floor interpretation unresolved: ATO guidance requires the benchmark interest rate for each year of the loan. This workbook compares one selected year's benchmark and defaults to the year the loan was made. COMPLYING does not establish that the agreement meets the annual interest requirement. Review the agreement and relevant years before relying on this result. See docs/primary-source-review-2026-08-31.md. The lodgment day (s 109D(6)) is asserted, not computed. Refinancing reductions to the maximum term (s 109N(3A) to (3D)) and the other Subdivision D exclusions are not modelled.</t>
   </si>
   <si>
     <t>s 109R: the workbook does not decide whether the payments applied are genuine repayments. The figure used is the operator's assertion.</t>
@@ -2756,7 +2756,7 @@
         <v>121</v>
       </c>
       <c r="B4" s="9" t="str">
-        <f>IF(ISNUMBER(Summary!B3),"PASS","BLOCKED")</f>
+        <f>IFERROR(IF(AND(ISNUMBER(Summary!B3),COUNT(tblRates[rate])=ROWS(tblRates[rate]),MIN(tblRates[rate])&gt;=0,MAX(tblRates[rate])&lt;=1),"PASS","BLOCKED"),"BLOCKED")</f>
         <v>PASS</v>
       </c>
       <c r="C4" s="9" t="str">
@@ -2864,7 +2864,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>128</v>
       </c>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA084D99-9AAC-4EBC-B672-6DE10659BCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235D3489-AEE8-4029-9C94-487CEFEC45FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -401,7 +401,7 @@
     <t>No formula in an input cell</t>
   </si>
   <si>
-    <t>A reviewed benchmark exists and every table rate is a number from zero to one</t>
+    <t>A reviewed benchmark exists, rate years are unique and rates are from zero to one</t>
   </si>
   <si>
     <t>Every reviewed loan is on s 109N terms</t>
@@ -2756,7 +2756,7 @@
         <v>121</v>
       </c>
       <c r="B4" s="9" t="str">
-        <f>IFERROR(IF(AND(ISNUMBER(Summary!B3),COUNT(tblRates[rate])=ROWS(tblRates[rate]),MIN(tblRates[rate])&gt;=0,MAX(tblRates[rate])&lt;=1),"PASS","BLOCKED"),"BLOCKED")</f>
+        <f>IFERROR(IF(AND(ISNUMBER(Summary!B3),COUNT(tblRates[rate])=ROWS(tblRates[rate]),SUMPRODUCT(--(COUNTIF(tblRates[year_of_income],tblRates[year_of_income])&lt;&gt;1))=0,MIN(tblRates[rate])&gt;=0,MAX(tblRates[rate])&lt;=1),"PASS","BLOCKED"),"BLOCKED")</f>
         <v>PASS</v>
       </c>
       <c r="C4" s="9" t="str">

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235D3489-AEE8-4029-9C94-487CEFEC45FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0F81A0-04EF-404E-8CD4-A4F65CFA007C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.1.2. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 0.1.3. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -446,7 +446,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0F81A0-04EF-404E-8CD4-A4F65CFA007C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DAA400-1921-4237-86A9-527DE9E5DEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.1.3. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 0.1.4. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -446,7 +446,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DAA400-1921-4237-86A9-527DE9E5DEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9C2A8D-EFF4-4CA2-B3A4-A1B9462A8FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Review Checks" sheetId="5" r:id="rId5"/>
     <sheet name="Sources &amp; Version" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="RateYears">tblRates[year_of_income]</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -284,7 +287,7 @@
     <t>2019-05</t>
   </si>
   <si>
-    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2019; cross-checked against the published Division 7A benchmark rate table.</t>
+    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2019; cross-checked against the published Division 7A benchmark rate table. Automated comparison 23 September 2026: xl/worksheets/sheet1.xml!D736, series identifier D11.</t>
   </si>
   <si>
     <t>2026-08-28</t>
@@ -293,31 +296,31 @@
     <t>2020-05</t>
   </si>
   <si>
-    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2020; cross-checked against the published Division 7A benchmark rate table.</t>
+    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2020; cross-checked against the published Division 7A benchmark rate table. Automated comparison 23 September 2026: xl/worksheets/sheet1.xml!D748, series identifier D11.</t>
   </si>
   <si>
     <t>2021-05</t>
   </si>
   <si>
-    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2021; cross-checked against the published Division 7A benchmark rate table.</t>
+    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2021; cross-checked against the published Division 7A benchmark rate table. Automated comparison 23 September 2026: xl/worksheets/sheet1.xml!D760, series identifier D11.</t>
   </si>
   <si>
     <t>2022-05</t>
   </si>
   <si>
-    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2022; cross-checked against the published Division 7A benchmark rate table.</t>
+    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2022; cross-checked against the published Division 7A benchmark rate table. Automated comparison 23 September 2026: xl/worksheets/sheet1.xml!D772, series identifier D11.</t>
   </si>
   <si>
     <t>2023-05</t>
   </si>
   <si>
-    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2023; cross-checked against the published Division 7A benchmark rate table.</t>
+    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2023; cross-checked against the published Division 7A benchmark rate table. Automated comparison 23 September 2026: xl/worksheets/sheet1.xml!D784, series identifier D11.</t>
   </si>
   <si>
     <t>2024-05</t>
   </si>
   <si>
-    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2024; cross-checked against the published Division 7A benchmark rate table.</t>
+    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2024; cross-checked against the published Division 7A benchmark rate table. Automated comparison 23 September 2026: xl/worksheets/sheet1.xml!D796, series identifier D11.</t>
   </si>
   <si>
     <t>2025-26</t>
@@ -326,7 +329,7 @@
     <t>2025-05</t>
   </si>
   <si>
-    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2025 (8.37 per cent). June 2025 was 8.27 per cent and is not the benchmark rate: it was published after the year of income began.</t>
+    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2025 (8.37 per cent). June 2025 was 8.27 per cent and is not the benchmark rate: it was published after the year of income began. Automated comparison 23 September 2026: xl/worksheets/sheet1.xml!D808, series identifier D11.</t>
   </si>
   <si>
     <t>2026-27</t>
@@ -335,7 +338,7 @@
     <t>2026-05</t>
   </si>
   <si>
-    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2026; cross-checked against the published Division 7A benchmark rate table.</t>
+    <t>RBA statistical table F5 Indicator Lending Rates, series FILRHLBVS (Housing loans; Banks; Variable; Standard; Owner-occupier), figure for May 2026; cross-checked against the published Division 7A benchmark rate table. Automated comparison 23 September 2026: xl/worksheets/sheet1.xml!D820, series identifier D11.</t>
   </si>
   <si>
     <t>To review a year outside this table, add a row with the May RBA F5 FILRHLBVS figure and cite where you read it. A blank source is not a review.</t>
@@ -2677,19 +2680,12 @@
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="B2" xr:uid="{00000000-0002-0000-0300-000000000000}">
+      <formula1>RateYears</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000000000000}">
-          <x14:formula1>
-            <xm:f>Rates!$A$2:$A$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9C2A8D-EFF4-4CA2-B3A4-A1B9462A8FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCADA3D8-7F1E-47BB-A0D5-4DDDC5C79244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -464,7 +464,7 @@
     <t>Law source</t>
   </si>
   <si>
-    <t>https://www.legislation.gov.au/C1936A00027/latest/text</t>
+    <t>https://www.legislation.gov.au/C1936A00027/2026-07-01/text</t>
   </si>
   <si>
     <t>Benchmark rates</t>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCADA3D8-7F1E-47BB-A0D5-4DDDC5C79244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A343B9-BA30-4589-8A19-80F1D424C2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.1.4. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 0.1.5. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -449,7 +449,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.1.5</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A343B9-BA30-4589-8A19-80F1D424C2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5602AC-2D1F-441A-A40D-B6882D24FF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.1.5. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 0.1.6. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -449,7 +449,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.5</t>
+    <t>0.1.6</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5602AC-2D1F-441A-A40D-B6882D24FF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEF1D6C-F520-48A2-B9FD-4356743E2E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.1.6. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 0.2.0. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -449,7 +449,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>
@@ -491,7 +491,7 @@
     <t>Experimental review aid. Not a Division 7A determination, not an ATO assessment, and not tax, legal or financial advice.</t>
   </si>
   <si>
-    <t>Excel 16.0 build 20430</t>
+    <t>Excel 16.0 build 20527</t>
   </si>
 </sst>
 </file>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEF1D6C-F520-48A2-B9FD-4356743E2E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D73362-5F24-42C3-95CE-6300FBA1E771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="153">
   <si>
     <t>Division 7A loan review: s 109N terms and s 109E minimum yearly repayment</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>Sample_row</t>
+  </si>
+  <si>
+    <t>Year_made_text</t>
+  </si>
+  <si>
+    <t>Year_tested_text</t>
   </si>
   <si>
     <t>L-101</t>
@@ -676,8 +682,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLoans" displayName="tblLoans" ref="A1:AJ9">
-  <tableColumns count="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLoans" displayName="tblLoans" ref="A1:AL9">
+  <tableColumns count="38">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="loan_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="borrower_reference"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="year_loan_made"/>
@@ -693,10 +699,10 @@
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="out_of_scope_reason"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="year_of_income_being_tested"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Status">
-      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Floor_year">
-      <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Floor_rate">
       <calculatedColumnFormula>IFERROR(INDEX(tblRates[rate],MATCH(tblLoans[[#This Row],[Floor_year]],tblRates[year_of_income],0)),"")</calculatedColumnFormula>
@@ -720,10 +726,10 @@
       <calculatedColumnFormula>IF(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),"UNKNOWN",IF(tblLoans[[#This Row],[Allowed_term_raw]]="",IF(tblLoans[[#This Row],[maximum_term_years]]&lt;=7,"PASS","UNKNOWN"),IF(tblLoans[[#This Row],[maximum_term_years]]&lt;=tblLoans[[#This Row],[Allowed_term_raw]],"PASS","FAIL")))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Gate_verdict">
-      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Max_term_allowed">
-      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Term_used">
       <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),ROUNDUP(tblLoans[[#This Row],[remaining_term_years]],0),""))</calculatedColumnFormula>
@@ -732,10 +738,10 @@
       <calculatedColumnFormula>IF(AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),ISNUMBER(Summary!$B$3),Summary!$B$3&gt;0,ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&gt;0),ROUND(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]*Summary!$B$3/(1-(1/(1+Summary!$B$3))^tblLoans[[#This Row],[Term_used]]),2),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="MYR_verdict">
-      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="MYR_reason">
-      <calculatedColumnFormula>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="MYR_required">
       <calculatedColumnFormula>IF(OR(tblLoans[[#This Row],[MYR_verdict]]="MYR_MET",tblLoans[[#This Row],[MYR_verdict]]="MYR_SHORT"),tblLoans[[#This Row],[MYR_raw]],"")</calculatedColumnFormula>
@@ -753,10 +759,16 @@
       <calculatedColumnFormula>IF(OR(_xlfn.ISFORMULA(tblLoans[[#This Row],[loan_id]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[borrower_reference]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[year_loan_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[written_agreement]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[maximum_term_years]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[security_coverage_at_first_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[remaining_term_years]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[payments_applied_during_the_year]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[out_of_scope_reason]]),_xlfn.ISFORMULA(tblLoans[[#This Row],[year_of_income_being_tested]])),1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Input_problem">
-      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Sample_row">
-      <calculatedColumnFormula>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Year_made_text">
+      <calculatedColumnFormula>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Year_tested_text">
+      <calculatedColumnFormula>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1138,7 +1150,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AJ9"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1151,9 +1163,10 @@
     <col min="29" max="29" width="40" customWidth="1"/>
     <col min="30" max="32" width="14" customWidth="1"/>
     <col min="33" max="36" width="12" customWidth="1"/>
+    <col min="37" max="38" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -1262,31 +1275,37 @@
       <c r="AJ1" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL1" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" s="7">
         <v>7</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I2" s="7">
         <v>8.2699999999999996E-2</v>
@@ -1303,11 +1322,11 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P2" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</f>
         <v>2023-24</v>
       </c>
       <c r="Q2" s="9">
@@ -1339,11 +1358,11 @@
         <v>PASS</v>
       </c>
       <c r="X2" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</f>
         <v>COMPLYING</v>
       </c>
       <c r="Y2" s="9">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
+        <f>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
         <v>7</v>
       </c>
       <c r="Z2" s="9">
@@ -1355,11 +1374,11 @@
         <v>47212.37</v>
       </c>
       <c r="AB2" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>MYR_SHORT</v>
       </c>
       <c r="AC2" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD2" s="10">
@@ -1383,38 +1402,46 @@
         <v>0</v>
       </c>
       <c r="AI2" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ2" s="9">
-        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
+        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK2" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v>2023-24</v>
+      </c>
+      <c r="AL2" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" s="7">
         <v>7</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I3" s="7">
         <v>0.04</v>
@@ -1431,11 +1458,11 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P3" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</f>
         <v>2022-23</v>
       </c>
       <c r="Q3" s="9">
@@ -1467,11 +1494,11 @@
         <v>PASS</v>
       </c>
       <c r="X3" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</f>
         <v>NOT_COMPLYING</v>
       </c>
       <c r="Y3" s="9">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
+        <f>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
         <v>7</v>
       </c>
       <c r="Z3" s="9">
@@ -1483,11 +1510,11 @@
         <v>27640.06</v>
       </c>
       <c r="AB3" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC3" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is NOT_COMPLYING, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD3" s="10" t="str">
@@ -1511,38 +1538,46 @@
         <v>0</v>
       </c>
       <c r="AI3" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ3" s="9">
-        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
+        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK3" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v>2022-23</v>
+      </c>
+      <c r="AL3" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="F4" s="7">
         <v>7</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I4" s="7">
         <v>4.5199999999999997E-2</v>
@@ -1559,11 +1594,11 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P4" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</f>
         <v>2021-22</v>
       </c>
       <c r="Q4" s="9">
@@ -1595,11 +1630,11 @@
         <v>PASS</v>
       </c>
       <c r="X4" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</f>
         <v>UNKNOWN</v>
       </c>
       <c r="Y4" s="9">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
+        <f>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
         <v>7</v>
       </c>
       <c r="Z4" s="9">
@@ -1611,11 +1646,11 @@
         <v>28334.799999999999</v>
       </c>
       <c r="AB4" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC4" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is UNKNOWN, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD4" s="10" t="str">
@@ -1639,38 +1674,46 @@
         <v>0</v>
       </c>
       <c r="AI4" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ4" s="9">
-        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
+        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK4" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v>2021-22</v>
+      </c>
+      <c r="AL4" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5" s="7">
         <v>7</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I5" s="7">
         <v>8.77E-2</v>
@@ -1682,16 +1725,16 @@
         <v>5</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P5" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</f>
         <v>2024-25</v>
       </c>
       <c r="Q5" s="9">
@@ -1723,11 +1766,11 @@
         <v>PASS</v>
       </c>
       <c r="X5" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</f>
         <v>COMPLYING</v>
       </c>
       <c r="Y5" s="9">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
+        <f>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
         <v>7</v>
       </c>
       <c r="Z5" s="9">
@@ -1739,11 +1782,11 @@
         <v>22489.279999999999</v>
       </c>
       <c r="AB5" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>UNKNOWN</v>
       </c>
       <c r="AC5" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>payments applied not established</v>
       </c>
       <c r="AD5" s="10" t="str">
@@ -1767,38 +1810,46 @@
         <v>0</v>
       </c>
       <c r="AI5" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ5" s="9">
-        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
+        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK5" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v>2024-25</v>
+      </c>
+      <c r="AL5" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="7">
         <v>7</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I6" s="7">
         <v>5.3699999999999998E-2</v>
@@ -1815,11 +1866,11 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P6" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</f>
         <v>2019-20</v>
       </c>
       <c r="Q6" s="9">
@@ -1851,11 +1902,11 @@
         <v>PASS</v>
       </c>
       <c r="X6" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</f>
         <v>COMPLYING</v>
       </c>
       <c r="Y6" s="9">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
+        <f>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
         <v>7</v>
       </c>
       <c r="Z6" s="9">
@@ -1867,11 +1918,11 @@
         <v/>
       </c>
       <c r="AB6" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC6" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>nil remaining term under s 109E(6)</v>
       </c>
       <c r="AD6" s="10" t="str">
@@ -1895,35 +1946,43 @@
         <v>0</v>
       </c>
       <c r="AI6" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ6" s="9">
-        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
+        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK6" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v>2019-20</v>
+      </c>
+      <c r="AL6" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F7" s="7">
         <v>25</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H7" s="7">
         <v>1.0900000000000001</v>
@@ -1943,11 +2002,11 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>REVIEWED</v>
       </c>
       <c r="P7" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</f>
         <v>2020-21</v>
       </c>
       <c r="Q7" s="9">
@@ -1979,11 +2038,11 @@
         <v>FAIL</v>
       </c>
       <c r="X7" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</f>
         <v>NOT_COMPLYING</v>
       </c>
       <c r="Y7" s="9">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
+        <f>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
         <v>7</v>
       </c>
       <c r="Z7" s="9">
@@ -1995,11 +2054,11 @@
         <v>36713.81</v>
       </c>
       <c r="AB7" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v>REFUSED</v>
       </c>
       <c r="AC7" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v>s 109N gate is NOT_COMPLYING, so s 109E produces no repayment figure</v>
       </c>
       <c r="AD7" s="10" t="str">
@@ -2023,61 +2082,69 @@
         <v>0</v>
       </c>
       <c r="AI7" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ7" s="9">
-        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
+        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK7" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v>2020-21</v>
+      </c>
+      <c r="AL7" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>SKIPPED</v>
       </c>
       <c r="P8" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</f>
         <v>2023-24</v>
       </c>
       <c r="Q8" s="9">
@@ -2109,11 +2176,11 @@
         <v>UNKNOWN</v>
       </c>
       <c r="X8" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</f>
         <v/>
       </c>
       <c r="Y8" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
+        <f>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
         <v/>
       </c>
       <c r="Z8" s="9" t="str">
@@ -2125,11 +2192,11 @@
         <v/>
       </c>
       <c r="AB8" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v/>
       </c>
       <c r="AC8" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD8" s="10" t="str">
@@ -2153,38 +2220,46 @@
         <v>0</v>
       </c>
       <c r="AI8" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ8" s="9">
-        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
+        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK8" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v>2023-24</v>
+      </c>
+      <c r="AL8" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F9" s="7">
         <v>7</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I9" s="7">
         <v>7.0000000000000007E-2</v>
@@ -2201,11 +2276,11 @@
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","SKIPPED",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;1998,FALSE),"SKIPPED","REVIEWED"))</f>
         <v>SKIPPED</v>
       </c>
       <c r="P9" s="9" t="str">
-        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))</f>
+        <f>IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),tblLoans[[#This Row],[Year_made_text]],tblLoans[[#This Row],[Year_tested_text]])</f>
         <v>1996-97</v>
       </c>
       <c r="Q9" s="9" t="str">
@@ -2237,11 +2312,11 @@
         <v>PASS</v>
       </c>
       <c r="X9" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING")))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"UNKNOWN",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="FAIL",tblLoans[[#This Row],[Limb_lodgment]]="FAIL",tblLoans[[#This Row],[Limb_b_rate]]="FAIL",tblLoans[[#This Row],[Limb_c_term]]="FAIL"),"NOT_COMPLYING",IF(OR(tblLoans[[#This Row],[Limb_a_written]]="UNKNOWN",tblLoans[[#This Row],[Limb_lodgment]]="UNKNOWN",tblLoans[[#This Row],[Limb_b_rate]]="UNKNOWN",tblLoans[[#This Row],[Limb_c_term]]="UNKNOWN"),"UNKNOWN","COMPLYING"))))</f>
         <v/>
       </c>
       <c r="Y9" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
+        <f>IF(OR(tblLoans[[#This Row],[Status]]="SKIPPED",OR(LOWER(TRIM(tblLoans[[#This Row],[Floor_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),"",IF(tblLoans[[#This Row],[Allowed_term_raw]]&lt;&gt;"",tblLoans[[#This Row],[Allowed_term_raw]],IF(AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),tblLoans[[#This Row],[maximum_term_years]]&lt;=7),7,"")))</f>
         <v/>
       </c>
       <c r="Z9" s="9" t="str">
@@ -2253,11 +2328,11 @@
         <v/>
       </c>
       <c r="AB9" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")),TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
+        <f>IF(tblLoans[[#This Row],[Status]]="SKIPPED","",IF(OR(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]]),tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),AND(ISNUMBER(Summary!$B$3),Summary!$B$3&lt;=0)),"REFUSED",IF(OR(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),NOT(ISNUMBER(Summary!$B$3)),NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),NOT(ISNUMBER(tblLoans[[#This Row],[Term_used]]))),"UNKNOWN",IF(tblLoans[[#This Row],[MYR_raw]]-ROUND(tblLoans[[#This Row],[payments_applied_during_the_year]],2)&lt;=0,"MYR_MET","MYR_SHORT"))))</f>
         <v/>
       </c>
       <c r="AC9" s="9" t="str">
-        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),"gate benchmark year differs from year_loan_made",IF(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;"")=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
+        <f>IF(tblLoans[[#This Row],[MYR_verdict]]="REFUSED",IF(tblLoans[[#This Row],[Gate_verdict]]&lt;&gt;"COMPLYING","s 109N gate is "&amp;tblLoans[[#This Row],[Gate_verdict]]&amp;", so s 109E produces no repayment figure",IF(tblLoans[[#This Row],[Floor_year]]&lt;&gt;tblLoans[[#This Row],[Year_made_text]],"gate benchmark year differs from year_loan_made",IF(tblLoans[[#This Row],[Year_made_text]]=Summary!$B$2,"year of income is the year the loan was made (s 109E(1)(a), s 109P)",IF(IFERROR(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;Summary!$B$4,FALSE),"loan made after the year of income",IF(AND(ISNUMBER(tblLoans[[#This Row],[Term_used]]),tblLoans[[#This Row],[Term_used]]&lt;=0),"nil remaining term under s 109E(6)","nil benchmark rate"))))),IF(tblLoans[[#This Row],[MYR_verdict]]="UNKNOWN",IF(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"}),"year_loan_made not established",IF(NOT(ISNUMBER(Summary!$B$3)),"no reviewed benchmark rate for the year of income",IF(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),"unpaid balance at end of previous year not established",IF(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),"payments applied not established","remaining term not established")))),""))</f>
         <v/>
       </c>
       <c r="AD9" s="10" t="str">
@@ -2281,12 +2356,20 @@
         <v>0</v>
       </c>
       <c r="AI9" s="9" t="str">
-        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_loan_made]]&amp;""),4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""))=7,MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),5,1)="-",ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),1,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),3,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),6,1))),ISNUMBER(VALUE(MID(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),7,1))),VALUE(RIGHT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),2))=MOD(VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))+1,100),VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&gt;=1900,VALUE(LEFT(TRIM(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;""),4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
+        <f>IF(TRIM(tblLoans[[#This Row],[out_of_scope_reason]]&amp;"")&lt;&gt;"","",TRIM(IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_made_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_made_text]])=7,MID(tblLoans[[#This Row],[Year_made_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_made_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_made_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_made_text]],4))&lt;=2100),FALSE))),AND(tblLoans[[#This Row],[Status]]="REVIEWED",AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[Year_tested_text]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(IFERROR(AND(LEN(tblLoans[[#This Row],[Year_tested_text]])=7,MID(tblLoans[[#This Row],[Year_tested_text]],5,1)="-",ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],1,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],2,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],3,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],4,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],6,1))),ISNUMBER(VALUE(MID(tblLoans[[#This Row],[Year_tested_text]],7,1))),VALUE(RIGHT(tblLoans[[#This Row],[Year_tested_text]],2))=MOD(VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))+1,100),VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&gt;=1900,VALUE(LEFT(tblLoans[[#This Row],[Year_tested_text]],4))&lt;=2100),FALSE))))),"year label ","")&amp;IF(tblLoans[[#This Row],[Status]]&lt;&gt;"REVIEWED","",IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[written_agreement]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[terms_in_place_before_lodgment_day]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"}))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[secured_by_registered_mortgage_over_real_property]]&amp;""))={"0","1","f","false","n","no","t","true","y","yes"})))),"true/false/unknown ","")&amp;IF(OR(AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[maximum_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[maximum_term_years]]),OR(tblLoans[[#This Row],[maximum_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[security_coverage_at_first_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]])),AND(ISNUMBER(tblLoans[[#This Row],[security_coverage_at_first_made]]),OR(tblLoans[[#This Row],[security_coverage_at_first_made]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]])),AND(ISNUMBER(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]),OR(tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&lt;0,tblLoans[[#This Row],[interest_rate_for_years_after_year_loan_made]]&gt;1)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])),AND(ISNUMBER(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),OR(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]]),N(tblLoans[[#This Row],[amalgamated_loan_unpaid_at_end_of_previous_year]])&gt;1000000000000)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[remaining_term_years]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]])),AND(ISNUMBER(tblLoans[[#This Row],[remaining_term_years]]),OR(tblLoans[[#This Row],[remaining_term_years]]&lt;0)))),AND(NOT(OR(LOWER(TRIM(tblLoans[[#This Row],[payments_applied_during_the_year]]&amp;""))={"","-","?","n/a","na","unk","unknown"})),OR(NOT(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]])),AND(ISNUMBER(tblLoans[[#This Row],[payments_applied_during_the_year]]),OR(tblLoans[[#This Row],[payments_applied_during_the_year]]&lt;0,ROUND(N(tblLoans[[#This Row],[payments_applied_during_the_year]]),2)&lt;&gt;N(tblLoans[[#This Row],[payments_applied_during_the_year]]),N(tblLoans[[#This Row],[payments_applied_during_the_year]])&gt;1000000000000))))),"number ",""))))</f>
         <v/>
       </c>
       <c r="AJ9" s="9">
-        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[year_loan_made]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
+        <f>IF(SUMPRODUCT((tblLoans[[#This Row],[loan_id]]&amp;""={"L-101","L-102","L-103","L-104","L-105","L-106","L-107","L-108"})*(tblLoans[[#This Row],[Year_made_text]]&amp;""={"2023-24","2022-23","2021-22","2024-25","2019-20","2020-21","2023-24","1996-97"}))&gt;0,1,0)</f>
         <v>1</v>
+      </c>
+      <c r="AK9" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_loan_made]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v>1996-97</v>
+      </c>
+      <c r="AL9" s="9" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(tblLoans[[#This Row],[year_of_income_being_tested]]&amp;"",_xlfn.UNICHAR(9)," "),_xlfn.UNICHAR(10)," "),_xlfn.UNICHAR(11)," "),_xlfn.UNICHAR(12)," "),_xlfn.UNICHAR(13)," "),_xlfn.UNICHAR(28)," "),_xlfn.UNICHAR(29)," "),_xlfn.UNICHAR(30)," "),_xlfn.UNICHAR(31)," "),_xlfn.UNICHAR(133)," "),_xlfn.UNICHAR(160)," "),_xlfn.UNICHAR(5760)," "),_xlfn.UNICHAR(8192)," "),_xlfn.UNICHAR(8193)," "),_xlfn.UNICHAR(8194)," "),_xlfn.UNICHAR(8195)," "),_xlfn.UNICHAR(8196)," "),_xlfn.UNICHAR(8197)," "),_xlfn.UNICHAR(8198)," "),_xlfn.UNICHAR(8199)," "),_xlfn.UNICHAR(8200)," "),_xlfn.UNICHAR(8201)," "),_xlfn.UNICHAR(8202)," "),_xlfn.UNICHAR(8232)," "),_xlfn.UNICHAR(8233)," "),_xlfn.UNICHAR(8239)," "),_xlfn.UNICHAR(8287)," "),_xlfn.UNICHAR(12288)," "))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2312,214 +2395,214 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B2" s="7">
         <v>5.3699999999999998E-2</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B3" s="7">
         <v>4.5199999999999997E-2</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="7">
         <v>4.5199999999999997E-2</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B5" s="7">
         <v>4.7699999999999999E-2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" s="7">
         <v>8.2699999999999996E-2</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B7" s="7">
         <v>8.77E-2</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B8" s="7">
         <v>8.3699999999999997E-2</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" s="7">
         <v>8.77E-2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2541,21 +2624,21 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B3" s="12">
         <f>IFERROR(INDEX(tblRates[rate],MATCH(B2,tblRates[year_of_income],0)),"")</f>
@@ -2564,7 +2647,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B4" s="9">
         <f>IFERROR(VALUE(LEFT(B2,4)),"")</f>
@@ -2573,13 +2656,13 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B7" s="9">
         <f>COUNTIF(tblLoans[Status],"REVIEWED")</f>
@@ -2588,7 +2671,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B8" s="9">
         <f>COUNTIF(tblLoans[Gate_verdict],"COMPLYING")</f>
@@ -2597,7 +2680,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B9" s="9">
         <f>COUNTIF(tblLoans[Gate_verdict],"NOT_COMPLYING")</f>
@@ -2606,7 +2689,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B10" s="9">
         <f>COUNTIF(tblLoans[MYR_verdict],"MYR_MET")</f>
@@ -2615,7 +2698,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B11" s="9">
         <f>COUNTIF(tblLoans[MYR_verdict],"MYR_SHORT")</f>
@@ -2624,7 +2707,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B12" s="9">
         <f>SUM(tblLoans[Undecided])</f>
@@ -2633,7 +2716,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B13" s="9">
         <f>COUNTIF(tblLoans[MYR_verdict],"REFUSED")</f>
@@ -2642,7 +2725,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B14" s="9">
         <f>COUNTIF(tblLoans[Status],"SKIPPED")</f>
@@ -2651,7 +2734,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B15" s="10">
         <f>SUM(tblLoans[Exposure])</f>
@@ -2701,21 +2784,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2" s="9" t="str">
         <f>IF(C2=0,"PASS","BLOCKED")</f>
@@ -2732,7 +2815,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B3" s="9" t="str">
         <f>IF(C3=0,"PASS","BLOCKED")</f>
@@ -2749,7 +2832,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B4" s="9" t="str">
         <f>IFERROR(IF(AND(ISNUMBER(Summary!B3),COUNT(tblRates[rate])=ROWS(tblRates[rate]),SUMPRODUCT(--(COUNTIF(tblRates[year_of_income],tblRates[year_of_income])&lt;&gt;1))=0,MIN(tblRates[rate])&gt;=0,MAX(tblRates[rate])&lt;=1),"PASS","BLOCKED"),"BLOCKED")</f>
@@ -2763,7 +2846,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B5" s="9" t="str">
         <f>IF(C5=0,"PASS","REVIEW")</f>
@@ -2780,7 +2863,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B6" s="9" t="str">
         <f>IF(C6=0,"PASS","REVIEW")</f>
@@ -2797,7 +2880,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B7" s="9" t="str">
         <f>IF(C7=0,"PASS","REVIEW")</f>
@@ -2814,7 +2897,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="9" t="str">
         <f>IF(C8=0,"PASS","REVIEW")</f>
@@ -2831,7 +2914,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" s="9" t="str">
         <f>IF(C9=0,"PASS","REVIEW")</f>
@@ -2857,32 +2940,32 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2913,82 +2996,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D73362-5F24-42C3-95CE-6300FBA1E771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A15B128-1B2D-4AF4-BC2E-9ADE5673B2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.2.0. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 0.3.0. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -455,7 +455,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A15B128-1B2D-4AF4-BC2E-9ADE5673B2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE97A878-B4CA-4B8D-9FBA-1A6F81E2BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.3.0. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 0.3.1. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -455,7 +455,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.3.1</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE97A878-B4CA-4B8D-9FBA-1A6F81E2BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A9D7CE-7C4F-4749-A564-608E431E2120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.3.1. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 0.3.2. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -455,7 +455,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.3.1</t>
+    <t>0.3.2</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>

--- a/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
+++ b/packages/div7a-loan-review/workbooks/div7a-loan-review.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A9D7CE-7C4F-4749-A564-608E431E2120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACFA53C-BE62-4172-8FC7-F9AAAE8BEC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-210" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>div7a-loan-review workbook, engine 0.3.2. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>div7a-loan-review workbook, engine 1.0.0. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>loan_id</t>
@@ -455,7 +455,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.3.2</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>
@@ -520,27 +520,37 @@
       <sz val="14"/>
       <color rgb="FF5C2D91"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F4E9E"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -553,16 +563,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F1F6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5C2D91"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2E0DF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -607,64 +620,64 @@
   <dxfs count="9">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD4EDDA"/>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3CD"/>
+        <patternFill>
+          <bgColor rgb="FFFFF3CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8D7DA"/>
+        <patternFill>
+          <bgColor rgb="FFF8D7DA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD4EDDA"/>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3CD"/>
+        <patternFill>
+          <bgColor rgb="FFFFF3CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8D7DA"/>
+        <patternFill>
+          <bgColor rgb="FFF8D7DA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD4EDDA"/>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3CD"/>
+        <patternFill>
+          <bgColor rgb="FFFFF3CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8D7DA"/>
+        <patternFill>
+          <bgColor rgb="FFF8D7DA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -682,7 +695,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLoans" displayName="tblLoans" ref="A1:AL9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLoans" displayName="tblLoans" ref="A1:AL9" totalsRowShown="0">
   <tableColumns count="38">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="loan_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="borrower_reference"/>
@@ -776,7 +789,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblRates" displayName="tblRates" ref="A1:G9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblRates" displayName="tblRates" ref="A1:G9" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="year_of_income"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="rate"/>
@@ -791,9 +804,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -831,7 +844,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -865,6 +878,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -899,9 +913,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1145,6 +1160,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
@@ -2379,6 +2395,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -2607,6 +2624,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -2769,6 +2787,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
@@ -2982,6 +3001,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
@@ -3076,5 +3096,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>